--- a/QUOTATION_EXCEL_TEMPLATES/la_kr_air_exp/LA_KR_AIR_EXP_2026_QUOTATION.xlsx
+++ b/QUOTATION_EXCEL_TEMPLATES/la_kr_air_exp/LA_KR_AIR_EXP_2026_QUOTATION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\다른 컴퓨터\내 컴퓨터\LK Group 관련\3. 라오-한국(및 기타) 항공 관련\고객 견적 확인 요청건\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\lkgroup_app\QUOTATION_EXCEL_TEMPLATES\la_kr_air_exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BE5106-3DAB-4BC2-B2C5-DBA921F04A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FF8AB4-E1CE-483F-B803-DB6C2F8A5994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="1005" windowWidth="17775" windowHeight="13770" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Row data" sheetId="3" r:id="rId1"/>
@@ -1250,10 +1250,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lao-Kor Air 가견적</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>- 동 가견적 운임의 중량 및 크기는 단순 예상치이므로 최종 책정 방법인 기준인 실측시 금액 차이가 발생 할수 있으니, 참고용으로만 확인 부탁 드립니다.
 - 운임은 USD 기준이며, 이외 화폐는 가견적 안내시의 환율 기준이므로, 최종 운임 책정시의 환율변동으로 인한 운임 차이가 발생할수 있으니, 참고용으로만 확인 부탁 드립니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1265,6 +1261,10 @@
   <si>
     <t>* 물품 출고 후 1주 후부터 보관료(최소 3불/CBM/day)가 발생하며, 특별한 사유 없이 2달 이상 보관 물품들은 임의로 폐기/처분 될 수 있습니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lao-Kor Air 가견적서</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2143,6 +2143,96 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="9" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="8" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2173,15 +2263,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2189,15 +2270,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -2209,90 +2281,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="9" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="8" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2300,6 +2288,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2317,18 +2317,11 @@
     <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="표준 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2382,7 +2375,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$20:$G$38" spid="_x0000_s5156"/>
+                  <a14:cameraTool cellRange="$A$20:$G$38" spid="_x0000_s5157"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2596,8 +2589,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="50800" y="12369800"/>
-          <a:ext cx="8229600" cy="3733800"/>
+          <a:off x="50800" y="12465050"/>
+          <a:ext cx="8280400" cy="3727450"/>
           <a:chOff x="50800" y="15240000"/>
           <a:chExt cx="7899400" cy="3733800"/>
         </a:xfrm>
@@ -2728,8 +2721,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10261600" y="12344400"/>
-          <a:ext cx="7975600" cy="3719369"/>
+          <a:off x="10312400" y="12439650"/>
+          <a:ext cx="8020050" cy="3719369"/>
           <a:chOff x="9118600" y="15214600"/>
           <a:chExt cx="7975600" cy="3719369"/>
         </a:xfrm>
@@ -2866,8 +2859,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="20193000" y="12344399"/>
-          <a:ext cx="8026400" cy="3747978"/>
+          <a:off x="20294600" y="12439649"/>
+          <a:ext cx="8039100" cy="3747978"/>
           <a:chOff x="19761200" y="15214599"/>
           <a:chExt cx="8026400" cy="3747978"/>
         </a:xfrm>
@@ -3006,7 +2999,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s2117"/>
+                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s2118"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -3395,49 +3388,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:Y64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="4.19921875" style="35" customWidth="1"/>
-    <col min="2" max="2" width="15.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.19921875" style="35" customWidth="1"/>
-    <col min="4" max="5" width="11.3984375" style="35" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.25" style="35" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="35" customWidth="1"/>
+    <col min="4" max="5" width="11.375" style="35" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" style="35" customWidth="1"/>
-    <col min="7" max="7" width="6.09765625" style="35" customWidth="1"/>
+    <col min="7" max="7" width="6.125" style="35" customWidth="1"/>
     <col min="8" max="8" width="15" style="35" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.59765625" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.59765625" style="49" customWidth="1"/>
-    <col min="14" max="14" width="7.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.8984375" style="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.09765625" style="49" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.19921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.625" style="35" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.625" style="49" customWidth="1"/>
+    <col min="14" max="14" width="7.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.125" style="49" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.25" style="49" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="2.5" style="49" customWidth="1"/>
-    <col min="21" max="21" width="27.69921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.75" style="49" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22.5" style="49" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.19921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.25" style="49" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:25">
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="H1" s="148" t="s">
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="H1" s="144" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
     </row>
     <row r="2" spans="2:25">
       <c r="B2" s="36" t="s">
@@ -3472,24 +3465,24 @@
         <f>C3+D3</f>
         <v>24000</v>
       </c>
-      <c r="H3" s="143" t="s">
+      <c r="H3" s="146" t="s">
         <v>209</v>
       </c>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="N3" s="143" t="s">
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="N3" s="146" t="s">
         <v>180</v>
       </c>
-      <c r="O3" s="143"/>
-      <c r="P3" s="143"/>
-      <c r="Q3" s="143"/>
-      <c r="U3" s="143" t="s">
+      <c r="O3" s="146"/>
+      <c r="P3" s="146"/>
+      <c r="Q3" s="146"/>
+      <c r="U3" s="146" t="s">
         <v>181</v>
       </c>
-      <c r="V3" s="143"/>
-      <c r="W3" s="143"/>
-      <c r="X3" s="143"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
     </row>
     <row r="4" spans="2:25">
       <c r="B4" s="40" t="s">
@@ -3505,31 +3498,31 @@
         <f>C4+D4</f>
         <v>34</v>
       </c>
-      <c r="H4" s="144" t="s">
+      <c r="H4" s="147" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="145"/>
-      <c r="J4" s="144" t="s">
+      <c r="I4" s="148"/>
+      <c r="J4" s="147" t="s">
         <v>64</v>
       </c>
-      <c r="K4" s="145"/>
+      <c r="K4" s="148"/>
       <c r="L4" s="49"/>
-      <c r="N4" s="144" t="s">
+      <c r="N4" s="147" t="s">
         <v>63</v>
       </c>
-      <c r="O4" s="145"/>
-      <c r="P4" s="144" t="s">
+      <c r="O4" s="148"/>
+      <c r="P4" s="147" t="s">
         <v>64</v>
       </c>
-      <c r="Q4" s="145"/>
-      <c r="U4" s="144" t="s">
+      <c r="Q4" s="148"/>
+      <c r="U4" s="147" t="s">
         <v>63</v>
       </c>
-      <c r="V4" s="145"/>
-      <c r="W4" s="144" t="s">
+      <c r="V4" s="148"/>
+      <c r="W4" s="147" t="s">
         <v>64</v>
       </c>
-      <c r="X4" s="145"/>
+      <c r="X4" s="148"/>
     </row>
     <row r="5" spans="2:25">
       <c r="B5" s="42" t="s">
@@ -3870,10 +3863,10 @@
       <c r="Y12" s="61"/>
     </row>
     <row r="13" spans="2:25">
-      <c r="B13" s="147"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="147"/>
+      <c r="B13" s="143"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
       <c r="H13" s="36" t="s">
         <v>237</v>
       </c>
@@ -3908,10 +3901,10 @@
       <c r="Y13" s="61"/>
     </row>
     <row r="14" spans="2:25">
-      <c r="B14" s="147"/>
-      <c r="C14" s="147"/>
-      <c r="D14" s="147"/>
-      <c r="E14" s="147"/>
+      <c r="B14" s="143"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
       <c r="H14" s="36" t="s">
         <v>101</v>
       </c>
@@ -3950,12 +3943,12 @@
       </c>
     </row>
     <row r="15" spans="2:25">
-      <c r="B15" s="147" t="s">
+      <c r="B15" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="C15" s="147"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="147"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
       <c r="H15" s="36" t="s">
         <v>84</v>
       </c>
@@ -3992,12 +3985,12 @@
       <c r="Y15" s="61"/>
     </row>
     <row r="16" spans="2:25">
-      <c r="B16" s="147" t="s">
+      <c r="B16" s="143" t="s">
         <v>296</v>
       </c>
-      <c r="C16" s="147"/>
-      <c r="D16" s="147"/>
-      <c r="E16" s="147"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
       <c r="F16" s="45"/>
       <c r="H16" s="36" t="s">
         <v>90</v>
@@ -4199,11 +4192,11 @@
       </c>
       <c r="R21" s="61"/>
       <c r="S21" s="61"/>
-      <c r="U21" s="142" t="s">
+      <c r="U21" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="V21" s="142"/>
-      <c r="W21" s="142"/>
+      <c r="V21" s="145"/>
+      <c r="W21" s="145"/>
       <c r="X21" s="61">
         <f>SUM(X9:X20)</f>
         <v>0</v>
@@ -4301,12 +4294,12 @@
       </c>
       <c r="R24" s="61"/>
       <c r="S24" s="61"/>
-      <c r="U24" s="143" t="s">
+      <c r="U24" s="146" t="s">
         <v>182</v>
       </c>
-      <c r="V24" s="143"/>
-      <c r="W24" s="143"/>
-      <c r="X24" s="143"/>
+      <c r="V24" s="146"/>
+      <c r="W24" s="146"/>
+      <c r="X24" s="146"/>
       <c r="Y24" s="35"/>
     </row>
     <row r="25" spans="2:25">
@@ -4471,7 +4464,7 @@
       <c r="X28" s="61"/>
       <c r="Y28" s="47"/>
     </row>
-    <row r="29" spans="2:25" ht="76.8">
+    <row r="29" spans="2:25" ht="69">
       <c r="B29" s="35" t="s">
         <v>223</v>
       </c>
@@ -4611,11 +4604,11 @@
       </c>
       <c r="R32" s="61"/>
       <c r="S32" s="61"/>
-      <c r="U32" s="142" t="s">
+      <c r="U32" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="V32" s="142"/>
-      <c r="W32" s="142"/>
+      <c r="V32" s="145"/>
+      <c r="W32" s="145"/>
       <c r="X32" s="61">
         <f>SUM(X26:X31)</f>
         <v>0</v>
@@ -4967,12 +4960,12 @@
       </c>
       <c r="K46" s="51"/>
       <c r="L46" s="51"/>
-      <c r="N46" s="142" t="s">
+      <c r="N46" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="O46" s="142"/>
-      <c r="P46" s="142"/>
-      <c r="Q46" s="142"/>
+      <c r="O46" s="145"/>
+      <c r="P46" s="145"/>
+      <c r="Q46" s="145"/>
       <c r="R46" s="51">
         <f>SUM(R9:R45)</f>
         <v>0</v>
@@ -5143,11 +5136,11 @@
       <c r="L61" s="51"/>
     </row>
     <row r="62" spans="8:17">
-      <c r="H62" s="142" t="s">
+      <c r="H62" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="I62" s="142"/>
-      <c r="J62" s="142"/>
+      <c r="I62" s="145"/>
+      <c r="J62" s="145"/>
       <c r="K62" s="54">
         <f>SUM(K9:K59)</f>
         <v>0</v>
@@ -5175,13 +5168,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="20">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B16:E16"/>
     <mergeCell ref="H62:J62"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="N3:Q3"/>
@@ -5195,6 +5181,13 @@
     <mergeCell ref="U24:X24"/>
     <mergeCell ref="U32:W32"/>
     <mergeCell ref="N46:Q46"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B16:E16"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5210,10 +5203,10 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="55" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="95.09765625" style="55" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.625" style="55" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.125" style="55" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="68" style="55" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="55"/>
   </cols>
@@ -5386,7 +5379,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5397,47 +5390,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="28.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.3984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.8984375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="39.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="49.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="39.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.09765625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="16.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="39.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="49.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="30.8984375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="30.875" style="1" customWidth="1"/>
     <col min="19" max="19" width="9" style="1"/>
-    <col min="20" max="23" width="36.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="36.375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="132" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
+      <c r="C1" s="110" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
       <c r="L1" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="M1" s="128" t="s">
+      <c r="M1" s="106" t="s">
         <v>301</v>
       </c>
-      <c r="N1" s="129"/>
+      <c r="N1" s="107"/>
       <c r="R1" s="23">
         <f>D11</f>
         <v>1</v>
@@ -5455,33 +5448,33 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="2" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="120"/>
+      <c r="C2" s="96"/>
       <c r="D2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="130" t="s">
+      <c r="E2" s="108" t="s">
         <v>300</v>
       </c>
-      <c r="F2" s="130"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="106" t="s">
+      <c r="F2" s="108"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="97" t="s">
         <v>179</v>
       </c>
-      <c r="J2" s="107"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="138" t="s">
+      <c r="J2" s="98"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="M2" s="139"/>
-      <c r="N2" s="136"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="114"/>
       <c r="R2" s="24">
         <f>IFERROR(N16,0)</f>
         <v>18</v>
@@ -5501,25 +5494,25 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="3" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="120" t="s">
+      <c r="B3" s="96" t="s">
         <v>211</v>
       </c>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="140"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="137"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="115"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -5538,29 +5531,29 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="4" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="125" t="s">
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="126"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="133" t="s">
+      <c r="J4" s="104"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="M4" s="134"/>
-      <c r="N4" s="135"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="113"/>
       <c r="T4" s="33" t="s">
         <v>1</v>
       </c>
@@ -5576,7 +5569,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="5" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>10</v>
       </c>
@@ -5595,11 +5588,11 @@
       <c r="F5" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="G5" s="120" t="s">
+      <c r="G5" s="96" t="s">
         <v>231</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
       <c r="J5" s="22" t="s">
         <v>205</v>
       </c>
@@ -5616,7 +5609,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="6" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="22">
         <v>1</v>
       </c>
@@ -5667,7 +5660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="7" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="22">
         <v>2</v>
       </c>
@@ -5685,7 +5678,7 @@
       <c r="M7" s="21"/>
       <c r="N7" s="8"/>
     </row>
-    <row r="8" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="8" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="22">
         <v>3</v>
       </c>
@@ -5703,7 +5696,7 @@
       <c r="M8" s="21"/>
       <c r="N8" s="8"/>
     </row>
-    <row r="9" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="9" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="22">
         <v>4</v>
       </c>
@@ -5721,7 +5714,7 @@
       <c r="M9" s="21"/>
       <c r="N9" s="8"/>
     </row>
-    <row r="10" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="10" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="22">
         <v>5</v>
       </c>
@@ -5739,12 +5732,12 @@
       <c r="M10" s="21"/>
       <c r="N10" s="8"/>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A11" s="120" t="s">
+    <row r="11" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A11" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
       <c r="D11" s="4">
         <f>SUM(D6:D10)</f>
         <v>1</v>
@@ -5767,44 +5760,44 @@
       <c r="N11" s="13"/>
     </row>
     <row r="12" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A12" s="121" t="s">
+      <c r="A12" s="122" t="s">
         <v>212</v>
       </c>
-      <c r="B12" s="121"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121" t="s">
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122" t="s">
         <v>213</v>
       </c>
-      <c r="G12" s="121"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="120" t="s">
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="120"/>
+      <c r="M12" s="96"/>
       <c r="N12" s="76">
         <f>SUM(N6:N11)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A13" s="122" t="s">
-        <v>303</v>
-      </c>
-      <c r="B13" s="121"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
+    <row r="13" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A13" s="123" t="s">
+        <v>302</v>
+      </c>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="125"/>
+      <c r="K13" s="125"/>
       <c r="L13" s="84" t="s">
         <v>16</v>
       </c>
@@ -5817,18 +5810,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="121"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
-      <c r="K14" s="124"/>
+    <row r="14" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A14" s="122"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="125"/>
       <c r="L14" s="84" t="s">
         <v>233</v>
       </c>
@@ -5841,18 +5834,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="121"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="124"/>
-      <c r="J15" s="124"/>
-      <c r="K15" s="124"/>
+    <row r="15" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A15" s="122"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
       <c r="L15" s="84" t="s">
         <v>234</v>
       </c>
@@ -5866,18 +5859,18 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="124"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="118" t="s">
+      <c r="A16" s="122"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="125"/>
+      <c r="K16" s="125"/>
+      <c r="L16" s="120" t="s">
         <v>214</v>
       </c>
       <c r="M16" s="81" t="s">
@@ -5889,18 +5882,18 @@
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="119"/>
+      <c r="A17" s="122"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="125"/>
+      <c r="K17" s="125"/>
+      <c r="L17" s="121"/>
       <c r="M17" s="82" t="s">
         <v>18</v>
       </c>
@@ -5910,18 +5903,18 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="124"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="119"/>
+      <c r="A18" s="122"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="121"/>
       <c r="M18" s="83" t="s">
         <v>19</v>
       </c>
@@ -5930,19 +5923,19 @@
         <v>620</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A19" s="123"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="124"/>
-      <c r="I19" s="124"/>
-      <c r="J19" s="124"/>
-      <c r="K19" s="124"/>
-      <c r="L19" s="119"/>
+    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A19" s="124"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="125"/>
+      <c r="L19" s="121"/>
       <c r="M19" s="14" t="s">
         <v>20</v>
       </c>
@@ -5967,147 +5960,147 @@
       <c r="M20" s="86"/>
       <c r="N20" s="86"/>
     </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A21" s="98" t="s">
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A21" s="128" t="s">
         <v>208</v>
       </c>
-      <c r="B21" s="98"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-      <c r="N21" s="98"/>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A22" s="99" t="s">
+      <c r="B21" s="128"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="128"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="128"/>
+    </row>
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A22" s="129" t="s">
+        <v>303</v>
+      </c>
+      <c r="B22" s="129"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="129"/>
+      <c r="I22" s="129"/>
+      <c r="J22" s="129"/>
+      <c r="K22" s="129"/>
+      <c r="L22" s="129"/>
+      <c r="M22" s="129"/>
+      <c r="N22" s="129"/>
+    </row>
+    <row r="23" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A23" s="139" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="99"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="99"/>
-      <c r="H22" s="99"/>
-      <c r="I22" s="99"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="99"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="99"/>
-      <c r="N22" s="99"/>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A23" s="115" t="s">
-        <v>305</v>
-      </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="115"/>
-      <c r="L23" s="115"/>
-      <c r="M23" s="115"/>
-      <c r="N23" s="115"/>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A24" s="100" t="s">
+      <c r="B23" s="139"/>
+      <c r="C23" s="139"/>
+      <c r="D23" s="139"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="139"/>
+      <c r="G23" s="139"/>
+      <c r="H23" s="139"/>
+      <c r="I23" s="139"/>
+      <c r="J23" s="139"/>
+      <c r="K23" s="139"/>
+      <c r="L23" s="139"/>
+      <c r="M23" s="139"/>
+      <c r="N23" s="139"/>
+    </row>
+    <row r="24" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A24" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="101"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="108"/>
+      <c r="B24" s="131"/>
+      <c r="C24" s="97"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="99"/>
       <c r="F24" s="94"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="116" t="s">
+      <c r="H24" s="140" t="s">
         <v>216</v>
       </c>
-      <c r="I24" s="116"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="96" t="s">
+      <c r="I24" s="140"/>
+      <c r="J24" s="141"/>
+      <c r="K24" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="97"/>
-      <c r="M24" s="97"/>
-      <c r="N24" s="97"/>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="103"/>
-      <c r="C25" s="109"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="111"/>
+      <c r="L24" s="127"/>
+      <c r="M24" s="127"/>
+      <c r="N24" s="127"/>
+    </row>
+    <row r="25" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A25" s="132"/>
+      <c r="B25" s="133"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="138"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
       <c r="J25" s="95"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="97"/>
-      <c r="M25" s="97"/>
-      <c r="N25" s="97"/>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="103"/>
-      <c r="C26" s="109"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="111"/>
+      <c r="K25" s="126"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
+    </row>
+    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A26" s="132"/>
+      <c r="B26" s="133"/>
+      <c r="C26" s="136"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="138"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
-      <c r="K26" s="96"/>
-      <c r="L26" s="97"/>
-      <c r="M26" s="97"/>
-      <c r="N26" s="97"/>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="103"/>
-      <c r="C27" s="109"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="111"/>
+      <c r="K26" s="126"/>
+      <c r="L26" s="127"/>
+      <c r="M26" s="127"/>
+      <c r="N26" s="127"/>
+    </row>
+    <row r="27" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A27" s="132"/>
+      <c r="B27" s="133"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="138"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
-      <c r="K27" s="96"/>
-      <c r="L27" s="97"/>
-      <c r="M27" s="97"/>
-      <c r="N27" s="97"/>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A28" s="104"/>
-      <c r="B28" s="105"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="114"/>
+      <c r="K27" s="126"/>
+      <c r="L27" s="127"/>
+      <c r="M27" s="127"/>
+      <c r="N27" s="127"/>
+    </row>
+    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A28" s="134"/>
+      <c r="B28" s="135"/>
+      <c r="C28" s="100"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="102"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
-      <c r="K28" s="96"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
-      <c r="N28" s="97"/>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" ht="30">
+      <c r="K28" s="126"/>
+      <c r="L28" s="127"/>
+      <c r="M28" s="127"/>
+      <c r="N28" s="127"/>
+    </row>
+    <row r="29" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="16"/>
@@ -6123,7 +6116,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" ht="30">
+    <row r="30" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -6143,8 +6136,8 @@
     <row r="32" spans="1:14" ht="16.5" customHeight="1"/>
     <row r="33" spans="17:22" ht="16.5" customHeight="1"/>
     <row r="34" spans="17:22" ht="16.5" customHeight="1"/>
-    <row r="37" spans="17:22" ht="24.9" customHeight="1"/>
-    <row r="38" spans="17:22" ht="24.9" customHeight="1">
+    <row r="37" spans="17:22" ht="24.95" customHeight="1"/>
+    <row r="38" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q38" s="18"/>
       <c r="R38" s="18"/>
       <c r="S38" s="18"/>
@@ -6152,28 +6145,28 @@
       <c r="U38" s="18"/>
       <c r="V38" s="18"/>
     </row>
-    <row r="39" spans="17:22" ht="24.9" customHeight="1">
+    <row r="39" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q39" s="19"/>
     </row>
-    <row r="40" spans="17:22" ht="24.9" customHeight="1">
+    <row r="40" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q40" s="19"/>
     </row>
-    <row r="41" spans="17:22" ht="24.9" customHeight="1">
+    <row r="41" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q41" s="19"/>
     </row>
-    <row r="42" spans="17:22" ht="24.9" customHeight="1">
+    <row r="42" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q42" s="19"/>
     </row>
-    <row r="43" spans="17:22" ht="24.9" customHeight="1">
+    <row r="43" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q43" s="19"/>
     </row>
-    <row r="44" spans="17:22" ht="24.9" customHeight="1">
+    <row r="44" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q44" s="19"/>
     </row>
-    <row r="45" spans="17:22" ht="24.9" customHeight="1">
+    <row r="45" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q45" s="19"/>
     </row>
-    <row r="46" spans="17:22" ht="24.9" customHeight="1">
+    <row r="46" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q46" s="19"/>
     </row>
     <row r="47" spans="17:22" ht="30" customHeight="1"/>
@@ -6194,6 +6187,20 @@
     <row r="62" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="K24:K28"/>
+    <mergeCell ref="L24:N28"/>
+    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A24:B28"/>
+    <mergeCell ref="C24:E28"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E19"/>
+    <mergeCell ref="F12:K12"/>
+    <mergeCell ref="F13:K19"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="I2:K3"/>
     <mergeCell ref="I4:K4"/>
@@ -6207,24 +6214,10 @@
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L16:L19"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:E19"/>
-    <mergeCell ref="F12:K12"/>
-    <mergeCell ref="F13:K19"/>
-    <mergeCell ref="K24:K28"/>
-    <mergeCell ref="L24:N28"/>
-    <mergeCell ref="A21:N21"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="A24:B28"/>
-    <mergeCell ref="C24:E28"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="H24:J24"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="L6">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>N6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6234,7 +6227,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="27" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
